--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -758,13 +758,13 @@
         <v>0.8556701030927835</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8482142857142857</v>
+        <v>0.8392857142857143</v>
       </c>
       <c r="E14" t="n">
         <v>0.8613861386138614</v>
       </c>
       <c r="F14" t="n">
-        <v>0.8524826803989219</v>
+        <v>0.850250537541779</v>
       </c>
     </row>
     <row r="15">
@@ -777,16 +777,16 @@
         <v>0.4943181818181818</v>
       </c>
       <c r="C15" t="n">
-        <v>0.5265567765567766</v>
+        <v>0.4940476190476191</v>
       </c>
       <c r="D15" t="n">
-        <v>0.5945652173913043</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="E15" t="n">
         <v>0.5969101123595506</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5530875720314533</v>
+        <v>0.5484928913498162</v>
       </c>
     </row>
     <row r="16">
@@ -799,16 +799,16 @@
         <v>0.4578947368421052</v>
       </c>
       <c r="C16" t="n">
-        <v>0.5231741573033708</v>
+        <v>0.4611111111111111</v>
       </c>
       <c r="D16" t="n">
-        <v>0.617286432160804</v>
+        <v>0.6326530612244898</v>
       </c>
       <c r="E16" t="n">
         <v>0.6115384615384616</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5524734469611854</v>
+        <v>0.5407993426790419</v>
       </c>
     </row>
     <row r="17">
@@ -821,16 +821,16 @@
         <v>0.7824220746039856</v>
       </c>
       <c r="C17" t="n">
-        <v>0.8146212208965598</v>
+        <v>0.7986254295532647</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8083991385498923</v>
+        <v>0.8097667638483965</v>
       </c>
       <c r="E17" t="n">
         <v>0.8490479817212491</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8136226039429217</v>
+        <v>0.8099655624317239</v>
       </c>
     </row>
     <row r="18">
@@ -843,16 +843,16 @@
         <v>0.7799242424242423</v>
       </c>
       <c r="C18" t="n">
-        <v>0.6373626373626373</v>
+        <v>0.5865384615384616</v>
       </c>
       <c r="D18" t="n">
-        <v>0.6839673913043479</v>
+        <v>0.6448369565217391</v>
       </c>
       <c r="E18" t="n">
         <v>0.7612359550561798</v>
       </c>
       <c r="F18" t="n">
-        <v>0.7156225565368519</v>
+        <v>0.6931339038851558</v>
       </c>
     </row>
     <row r="19">
@@ -868,12 +868,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>[[82, 2], [12, 1]]</t>
+          <t>[[83, 1], [13, 0]]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>[[91, 1], [16, 4]]</t>
+          <t>[[89, 3], [15, 5]]</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1406,34 +1406,34 @@
         <v>413</v>
       </c>
       <c r="F4" t="n">
-        <v>0.8524826803989219</v>
+        <v>0.850250537541779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006496955354733349</v>
+        <v>0.008730014175190924</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5530875720314533</v>
+        <v>0.5484928913498162</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04415465558682397</v>
+        <v>0.05446968544531497</v>
       </c>
       <c r="J4" t="n">
-        <v>0.5524734469611854</v>
+        <v>0.5407993426790419</v>
       </c>
       <c r="K4" t="n">
-        <v>0.06613051447656625</v>
+        <v>0.0816463662189498</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8136226039429217</v>
+        <v>0.8099655624317239</v>
       </c>
       <c r="M4" t="n">
-        <v>0.02375243276118939</v>
+        <v>0.02456988682216944</v>
       </c>
       <c r="N4" t="n">
-        <v>0.7156225565368519</v>
+        <v>0.6931339038851558</v>
       </c>
       <c r="O4" t="n">
-        <v>0.05775368682494515</v>
+        <v>0.0804139846219892</v>
       </c>
       <c r="P4" t="inlineStr">
         <is>

--- a/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
+++ b/slide_classification/TCGA_Results/Caption_based_aggregation_15_classes/UNI2/1-MSIH/Output/cross_valid_avg_eval_metrics.xlsx
@@ -613,16 +613,16 @@
         <v>0.8543689320388349</v>
       </c>
       <c r="C8" t="n">
-        <v>0.865979381443299</v>
+        <v>0.8969072164948454</v>
       </c>
       <c r="D8" t="n">
         <v>0.8035714285714286</v>
       </c>
       <c r="E8" t="n">
-        <v>0.801980198019802</v>
+        <v>0.8316831683168316</v>
       </c>
       <c r="F8" t="n">
-        <v>0.8314749850183412</v>
+        <v>0.8466326863554852</v>
       </c>
     </row>
     <row r="9">
@@ -635,16 +635,16 @@
         <v>0.8041666666666667</v>
       </c>
       <c r="C9" t="n">
-        <v>0.76007326007326</v>
+        <v>0.7779304029304029</v>
       </c>
       <c r="D9" t="n">
         <v>0.8021739130434783</v>
       </c>
       <c r="E9" t="n">
-        <v>0.8155430711610487</v>
+        <v>0.7602996254681648</v>
       </c>
       <c r="F9" t="n">
-        <v>0.7954892277361134</v>
+        <v>0.7861426520271781</v>
       </c>
     </row>
     <row r="10">
@@ -657,16 +657,16 @@
         <v>0.7529185990724452</v>
       </c>
       <c r="C10" t="n">
-        <v>0.7364681295715778</v>
+        <v>0.7779304029304029</v>
       </c>
       <c r="D10" t="n">
         <v>0.7315904139433551</v>
       </c>
       <c r="E10" t="n">
-        <v>0.6882716049382716</v>
+        <v>0.6921283844360768</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7273121868814123</v>
+        <v>0.7386419500955701</v>
       </c>
     </row>
     <row r="11">
@@ -679,16 +679,16 @@
         <v>0.8651288158383005</v>
       </c>
       <c r="C11" t="n">
-        <v>0.871693113143522</v>
+        <v>0.8969072164948454</v>
       </c>
       <c r="D11" t="n">
         <v>0.8209461562402739</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8318054027624985</v>
+        <v>0.8501536544186963</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8473933719961487</v>
+        <v>0.858283960748029</v>
       </c>
     </row>
     <row r="12">
@@ -701,16 +701,16 @@
         <v>0.8909090909090909</v>
       </c>
       <c r="C12" t="n">
-        <v>0.8956043956043955</v>
+        <v>0.8983516483516485</v>
       </c>
       <c r="D12" t="n">
         <v>0.8869565217391304</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8829588014981274</v>
+        <v>0.8380149812734082</v>
       </c>
       <c r="F12" t="n">
-        <v>0.889107202437686</v>
+        <v>0.8785580605683195</v>
       </c>
     </row>
     <row r="13">
@@ -726,7 +726,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>[[76, 8], [5, 8]]</t>
+          <t>[[79, 5], [5, 8]]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -736,12 +736,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>[[71, 18], [2, 10]]</t>
+          <t>[[76, 13], [4, 8]]</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>[[74, 14], [4, 11]]</t>
+          <t>[[76, 12], [4, 11]]</t>
         </is>
       </c>
     </row>
@@ -1348,38 +1348,38 @@
         <v>413</v>
       </c>
       <c r="F3" t="n">
-        <v>0.8314749850183412</v>
+        <v>0.8466326863554852</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0289967114743338</v>
+        <v>0.03415090734350841</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7954892277361134</v>
+        <v>0.7861426520271781</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02107386038235567</v>
+        <v>0.01814641486943494</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7273121868814123</v>
+        <v>0.7386419500955701</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0238850889526044</v>
+        <v>0.03146681261515766</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8473933719961487</v>
+        <v>0.858283960748029</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02149106438833642</v>
+        <v>0.02738074803652617</v>
       </c>
       <c r="N3" t="n">
-        <v>0.889107202437686</v>
+        <v>0.8785580605683195</v>
       </c>
       <c r="O3" t="n">
-        <v>0.004687445538073559</v>
+        <v>0.02376241515800786</v>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>[[74, 14], [4, 11]]</t>
+          <t>[[76, 12], [4, 11]]</t>
         </is>
       </c>
     </row>
